--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T15:11:15+00:00</t>
+    <t>2026-09-14T07:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:29:46+00:00</t>
+    <t>2026-09-14T08:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:03:24+00:00</t>
+    <t>2026-09-14T11:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Level</t>
@@ -157,6 +157,15 @@
   </si>
   <si>
     <t>Library-Preparation Kit</t>
+  </si>
+  <si>
+    <t>gene-panel</t>
+  </si>
+  <si>
+    <t>Genpanel</t>
+  </si>
+  <si>
+    <t>Sequenzier-Panel-Produkt (Genpanel) — Katalogebene via DeviceDefinition-Template. TODO:REVIEW (2026-09-14 ergaenzt fuer den Panel-Katalog)</t>
   </si>
 </sst>
 </file>
@@ -466,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -519,6 +528,20 @@
       </c>
       <c r="D4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:48:09+00:00</t>
+    <t>2026-09-14T12:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:20:33+00:00</t>
+    <t>2026-09-14T12:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:53:39+00:00</t>
+    <t>2026-09-14T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-genomicanalysis-devicefunction.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:42:50+00:00</t>
+    <t>2026-09-14T17:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
